--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. ESTUDIANTES CARTAGENA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_C.B. ESTUDIANTES CARTAGENA.xlsx
@@ -565,13 +565,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>48.3899</v>
+        <v>54.3241</v>
       </c>
       <c r="E2" t="n">
-        <v>47.1604</v>
+        <v>54.9988</v>
       </c>
       <c r="F2" t="n">
-        <v>1.229499999999999</v>
+        <v>-0.6749000000000004</v>
       </c>
       <c r="G2" t="n">
         <v>64.5852</v>
@@ -610,13 +610,13 @@
         <v>40.9479</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8170000000000002</v>
+        <v>5.117</v>
       </c>
       <c r="T2" t="n">
-        <v>-9.24</v>
+        <v>-1.4017</v>
       </c>
       <c r="U2" t="n">
-        <v>8.423</v>
+        <v>6.5187</v>
       </c>
       <c r="V2" t="n">
         <v>32.3626</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CARR</t>
+          <t>A. FERRAGUT SEBASTIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>31.3263</v>
+        <v>31.9313</v>
       </c>
       <c r="E3" t="n">
-        <v>23.4066</v>
+        <v>33.4085</v>
       </c>
       <c r="F3" t="n">
-        <v>7.9194</v>
+        <v>-1.477300000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3122000000000007</v>
+        <v>27.0907</v>
       </c>
       <c r="H3" t="n">
-        <v>6.485100000000001</v>
+        <v>7.107999999999998</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.7974</v>
+        <v>19.9823</v>
       </c>
       <c r="J3" t="n">
-        <v>37.1783</v>
+        <v>57.0814</v>
       </c>
       <c r="K3" t="n">
-        <v>24.2419</v>
+        <v>24.727</v>
       </c>
       <c r="L3" t="n">
-        <v>12.9364</v>
+        <v>32.3543</v>
       </c>
       <c r="M3" t="n">
-        <v>-37.4905</v>
+        <v>-29.9906</v>
       </c>
       <c r="N3" t="n">
-        <v>-17.7566</v>
+        <v>-17.6186</v>
       </c>
       <c r="O3" t="n">
-        <v>-19.7337</v>
+        <v>-12.3721</v>
       </c>
       <c r="P3" t="n">
-        <v>-22.2666</v>
+        <v>-4.151400000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-67.932</v>
+        <v>-53.4021</v>
       </c>
       <c r="R3" t="n">
-        <v>45.6654</v>
+        <v>49.2507</v>
       </c>
       <c r="S3" t="n">
-        <v>20.5231</v>
+        <v>7.8783</v>
       </c>
       <c r="T3" t="n">
-        <v>9.071</v>
+        <v>1.5432</v>
       </c>
       <c r="U3" t="n">
-        <v>11.4521</v>
+        <v>6.3351</v>
       </c>
       <c r="V3" t="n">
-        <v>33.3814</v>
+        <v>1.113900000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>45.0889</v>
+        <v>28.1858</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.7075</v>
+        <v>-27.0719</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FERRAGUT SEBASTIA</t>
+          <t>J. CARR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,70 +718,70 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>29.1413</v>
+        <v>23.0827</v>
       </c>
       <c r="E4" t="n">
-        <v>32.8004</v>
+        <v>16.5695</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.659299999999999</v>
+        <v>6.5131</v>
       </c>
       <c r="G4" t="n">
-        <v>27.0907</v>
+        <v>-0.3122000000000007</v>
       </c>
       <c r="H4" t="n">
-        <v>7.107999999999998</v>
+        <v>6.485100000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>19.9823</v>
+        <v>-6.7974</v>
       </c>
       <c r="J4" t="n">
-        <v>57.0814</v>
+        <v>37.1783</v>
       </c>
       <c r="K4" t="n">
-        <v>24.727</v>
+        <v>24.2419</v>
       </c>
       <c r="L4" t="n">
-        <v>32.3543</v>
+        <v>12.9364</v>
       </c>
       <c r="M4" t="n">
-        <v>-29.9906</v>
+        <v>-37.4905</v>
       </c>
       <c r="N4" t="n">
-        <v>-17.6186</v>
+        <v>-17.7566</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.3721</v>
+        <v>-19.7337</v>
       </c>
       <c r="P4" t="n">
-        <v>-4.151400000000001</v>
+        <v>-22.2666</v>
       </c>
       <c r="Q4" t="n">
-        <v>-53.4021</v>
+        <v>-67.932</v>
       </c>
       <c r="R4" t="n">
-        <v>49.2507</v>
+        <v>45.6654</v>
       </c>
       <c r="S4" t="n">
-        <v>5.0884</v>
+        <v>12.28</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9351</v>
+        <v>2.2341</v>
       </c>
       <c r="U4" t="n">
-        <v>4.1529</v>
+        <v>10.0459</v>
       </c>
       <c r="V4" t="n">
-        <v>1.113900000000001</v>
+        <v>33.3814</v>
       </c>
       <c r="W4" t="n">
-        <v>28.1858</v>
+        <v>45.0889</v>
       </c>
       <c r="X4" t="n">
-        <v>-27.0719</v>
+        <v>-11.7075</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>H. RODRÍGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>8.842599999999997</v>
+        <v>7.805499999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.993999999999999</v>
+        <v>7.805499999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>4.848800000000001</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9668999999999994</v>
+        <v>7.805499999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>9.7668</v>
+        <v>3.4868</v>
       </c>
       <c r="I6" t="n">
-        <v>-10.7339</v>
+        <v>4.3189</v>
       </c>
       <c r="J6" t="n">
-        <v>17.0758</v>
+        <v>7.805499999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>18.3123</v>
+        <v>3.4868</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2365</v>
+        <v>4.3189</v>
       </c>
       <c r="M6" t="n">
-        <v>-18.0427</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-8.545500000000001</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.4971</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-6.038399999999999</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-34.5321</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>28.4937</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>23.0283</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>13.772</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>9.2567</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-7.180400000000001</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>7.678000000000001</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-14.8584</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. RODRÍGUEZ GUTIERREZ</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>7.805499999999999</v>
+        <v>3.8917</v>
       </c>
       <c r="E7" t="n">
-        <v>7.805499999999999</v>
+        <v>-4.4149</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>8.306900000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>7.805499999999999</v>
+        <v>-28.4684</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4868</v>
+        <v>-8.555300000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3189</v>
+        <v>-19.9131</v>
       </c>
       <c r="J7" t="n">
-        <v>7.805499999999999</v>
+        <v>11.8027</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4868</v>
+        <v>16.2257</v>
       </c>
       <c r="L7" t="n">
-        <v>4.3189</v>
+        <v>-4.422899999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-40.271</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-24.7808</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-15.4899</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>16.0395</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-34.3434</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>50.3829</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.7891</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-5.1364</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>6.9255</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>14.5317</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>23.262</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-8.7303</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>3.48</v>
+        <v>3.052500000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>2.704699999999999</v>
+        <v>3.505700000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7750999999999997</v>
+        <v>-0.4533</v>
       </c>
       <c r="G8" t="n">
         <v>-5.888299999999999</v>
@@ -1078,13 +1078,13 @@
         <v>24.531</v>
       </c>
       <c r="S8" t="n">
-        <v>4.985799999999999</v>
+        <v>4.5585</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0655</v>
+        <v>-0.2644</v>
       </c>
       <c r="U8" t="n">
-        <v>6.0514</v>
+        <v>4.8224</v>
       </c>
       <c r="V8" t="n">
         <v>-0.7124999999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. PAREDES PEREZ</t>
+          <t>S. SUAREZ BELLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,67 +1108,67 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2294</v>
+        <v>1.3341</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2116</v>
+        <v>2.1648</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4409</v>
+        <v>-0.8307</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6109</v>
+        <v>0.6796000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09950000000000003</v>
+        <v>1.7249</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7102999999999999</v>
+        <v>-1.0454</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.09699999999999998</v>
+        <v>2.321</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4703000000000002</v>
+        <v>2.1976</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5673999999999999</v>
+        <v>0.1234</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7078</v>
+        <v>-1.6413</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5698</v>
+        <v>-0.4727</v>
       </c>
       <c r="O9" t="n">
-        <v>1.2774</v>
+        <v>-1.1688</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5661</v>
+        <v>0.5661</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1322</v>
+        <v>-0.3774</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1844</v>
+        <v>-0.2134</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0175</v>
+        <v>-0.0805</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1668999999999999</v>
+        <v>-0.1329</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SUAREZ BELLO</t>
+          <t>T. SASTRE MIR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6269</v>
+        <v>1.0908</v>
       </c>
       <c r="E10" t="n">
-        <v>1.775</v>
+        <v>4.4876</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1482</v>
+        <v>-3.3972</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6796000000000001</v>
+        <v>0.5678999999999998</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7249</v>
+        <v>7.2608</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0454</v>
+        <v>-6.6932</v>
       </c>
       <c r="J10" t="n">
-        <v>2.321</v>
+        <v>10.5417</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1976</v>
+        <v>14.0335</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1234</v>
+        <v>-3.4915</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6413</v>
+        <v>-9.9739</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4727</v>
+        <v>-6.7725</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1688</v>
+        <v>-3.2016</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5661</v>
+        <v>4.1514</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.3774</v>
+        <v>-11.322</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9435</v>
+        <v>15.4734</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9206</v>
+        <v>1.3144</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4704</v>
+        <v>2.2308</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4503</v>
+        <v>-0.9164999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3018</v>
+        <v>-4.9428</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3018</v>
+        <v>3.037</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-7.9798</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. PAREDES PÉREZ</t>
+          <t>I. PAREDES PEREZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,61 +1264,61 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>0.617</v>
+        <v>0.7216000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.617</v>
+        <v>-0.6399999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.3616</v>
       </c>
       <c r="G11" t="n">
-        <v>0.617</v>
+        <v>0.6109</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0.09950000000000003</v>
       </c>
       <c r="I11" t="n">
-        <v>0.617</v>
+        <v>0.7102999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.617</v>
+        <v>-0.09699999999999998</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.4703000000000002</v>
       </c>
       <c r="L11" t="n">
-        <v>0.617</v>
+        <v>-0.5673999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.7078</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.5698</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.2774</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.6768</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.0877</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. SASTRE MIR</t>
+          <t>I. PAREDES PÉREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.008099999999999996</v>
+        <v>0.617</v>
       </c>
       <c r="E12" t="n">
-        <v>5.6353</v>
+        <v>0.617</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.6435</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5678999999999998</v>
+        <v>0.617</v>
       </c>
       <c r="H12" t="n">
-        <v>7.2608</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.6932</v>
+        <v>0.617</v>
       </c>
       <c r="J12" t="n">
-        <v>10.5417</v>
+        <v>0.617</v>
       </c>
       <c r="K12" t="n">
-        <v>14.0335</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.4915</v>
+        <v>0.617</v>
       </c>
       <c r="M12" t="n">
-        <v>-9.9739</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-6.7725</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.2016</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>4.1514</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.322</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>15.4734</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2156999999999997</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3784</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.1628</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.9428</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>3.037</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.9798</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4468</v>
+        <v>0.2781999999999982</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.804500000000001</v>
+        <v>-4.1673</v>
       </c>
       <c r="F13" t="n">
-        <v>5.357699999999999</v>
+        <v>4.4455</v>
       </c>
       <c r="G13" t="n">
-        <v>-28.4684</v>
+        <v>-0.9668999999999994</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.555300000000001</v>
+        <v>9.7668</v>
       </c>
       <c r="I13" t="n">
-        <v>-19.9131</v>
+        <v>-10.7339</v>
       </c>
       <c r="J13" t="n">
-        <v>11.8027</v>
+        <v>17.0758</v>
       </c>
       <c r="K13" t="n">
-        <v>16.2257</v>
+        <v>18.3123</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.422899999999999</v>
+        <v>-1.2365</v>
       </c>
       <c r="M13" t="n">
-        <v>-40.271</v>
+        <v>-18.0427</v>
       </c>
       <c r="N13" t="n">
-        <v>-24.7808</v>
+        <v>-8.545500000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>-15.4899</v>
+        <v>-9.4971</v>
       </c>
       <c r="P13" t="n">
-        <v>16.0395</v>
+        <v>-6.038399999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-34.3434</v>
+        <v>-34.5321</v>
       </c>
       <c r="R13" t="n">
-        <v>50.3829</v>
+        <v>28.4937</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.5496</v>
+        <v>14.4642</v>
       </c>
       <c r="T13" t="n">
-        <v>-9.526</v>
+        <v>5.6111</v>
       </c>
       <c r="U13" t="n">
-        <v>3.9761</v>
+        <v>8.853</v>
       </c>
       <c r="V13" t="n">
-        <v>14.5317</v>
+        <v>-7.180400000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>23.262</v>
+        <v>7.678000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.7303</v>
+        <v>-14.8584</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. SUMLJAK JERMANCIC</t>
+          <t>H. RIVAS OSETE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.9005</v>
+        <v>-2.513999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4439</v>
+        <v>-5.8112</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.4566</v>
+        <v>3.2974</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.7071</v>
+        <v>0.8651</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4946</v>
+        <v>-0.1182000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.2125</v>
+        <v>0.9830999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.1746</v>
+        <v>4.1361</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0423</v>
+        <v>2.5052</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.2168</v>
+        <v>1.6311</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5325</v>
+        <v>-3.2714</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5368999999999999</v>
+        <v>-2.6234</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9957</v>
+        <v>-0.6482000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-3.2079</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-10.5672</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>7.3593</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5708</v>
+        <v>-0.6656</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2693</v>
+        <v>-1.2292</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3016</v>
+        <v>0.5633999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6226</v>
+        <v>0.4946999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6226</v>
+        <v>-1.3541</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.1504</v>
+        <v>-3.3503</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8995000000000006</v>
+        <v>-1.1314</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.2508</v>
+        <v>-2.2191</v>
       </c>
       <c r="G15" t="n">
         <v>5.727</v>
@@ -1624,13 +1624,13 @@
         <v>8.8689</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5189999999999999</v>
+        <v>0.2805000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3417999999999999</v>
+        <v>-0.5738</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1773</v>
+        <v>0.8545</v>
       </c>
       <c r="V15" t="n">
         <v>-8.4146</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. RIVAS OSETE</t>
+          <t>E. SUMLJAK JERMANCIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>-4.6135</v>
+        <v>-3.5146</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.5136</v>
+        <v>-1.1902</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8999</v>
+        <v>-2.3244</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8651</v>
+        <v>-2.7071</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1182000000000001</v>
+        <v>-0.4946</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9830999999999999</v>
+        <v>-2.2125</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1361</v>
+        <v>-1.1746</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5052</v>
+        <v>0.0423</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6311</v>
+        <v>-1.2168</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.2714</v>
+        <v>-1.5325</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.6234</v>
+        <v>-0.5368999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6482000000000001</v>
+        <v>-0.9957</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.2079</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-10.5672</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>7.3593</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.7652</v>
+        <v>-0.1849000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.9313</v>
+        <v>-0.0156</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8339000000000001</v>
+        <v>-0.1693</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4946999999999999</v>
+        <v>-0.6226</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3541</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>-5.104800000000001</v>
+        <v>-4.3833</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.2173</v>
+        <v>-4.256</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8875000000000005</v>
+        <v>-0.1273000000000004</v>
       </c>
       <c r="G17" t="n">
         <v>0.06569999999999993</v>
@@ -1780,13 +1780,13 @@
         <v>2.8305</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3203</v>
+        <v>2.0419</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6734000000000001</v>
+        <v>0.6347</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6469</v>
+        <v>1.4069</v>
       </c>
       <c r="V17" t="n">
         <v>-3.094</v>
@@ -1813,13 +1813,13 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>-6.793</v>
+        <v>-6.7805</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.739</v>
+        <v>-4.1472</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.0542</v>
+        <v>-2.6333</v>
       </c>
       <c r="G18" t="n">
         <v>-9.8437</v>
@@ -1858,13 +1858,13 @@
         <v>7.1706</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4836</v>
+        <v>1.4963</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6814</v>
+        <v>1.2733</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.198</v>
+        <v>0.2231</v>
       </c>
       <c r="V18" t="n">
         <v>-2.7732</v>
@@ -1891,13 +1891,13 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>-9.5404</v>
+        <v>-6.833</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.248</v>
+        <v>-9.5916</v>
       </c>
       <c r="F19" t="n">
-        <v>1.7075</v>
+        <v>2.7587</v>
       </c>
       <c r="G19" t="n">
         <v>-7.2606</v>
@@ -1936,13 +1936,13 @@
         <v>6.7932</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.865</v>
+        <v>-1.1576</v>
       </c>
       <c r="T19" t="n">
-        <v>-3.4314</v>
+        <v>-1.7751</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4336</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3018</v>
@@ -1969,13 +1969,13 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>-12.1469</v>
+        <v>-9.1884</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.6297</v>
+        <v>-9.148100000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5169</v>
+        <v>-0.0401999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-11.0203</v>
@@ -2014,13 +2014,13 @@
         <v>6.793200000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.5795</v>
+        <v>0.3789</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.9095</v>
+        <v>-0.4279</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.67</v>
+        <v>0.8067</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6225999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>-15.4838</v>
+        <v>-13.7716</v>
       </c>
       <c r="E21" t="n">
-        <v>-12.7438</v>
+        <v>-12.2365</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7402</v>
+        <v>-1.5348</v>
       </c>
       <c r="G21" t="n">
         <v>-4.893</v>
@@ -2092,13 +2092,13 @@
         <v>14.1525</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.0811</v>
+        <v>-1.369</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.9198</v>
+        <v>-1.4123</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1617</v>
+        <v>0.04329999999999995</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4144</v>
@@ -2125,13 +2125,13 @@
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>-49.1955</v>
+        <v>-41.5549</v>
       </c>
       <c r="E22" t="n">
-        <v>-56.9248</v>
+        <v>-52.1273</v>
       </c>
       <c r="F22" t="n">
-        <v>7.7293</v>
+        <v>10.5721</v>
       </c>
       <c r="G22" t="n">
         <v>-23.8744</v>
@@ -2170,13 +2170,13 @@
         <v>34.1547</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.3218</v>
+        <v>2.318700000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-7.0234</v>
+        <v>-2.2257</v>
       </c>
       <c r="U22" t="n">
-        <v>1.7015</v>
+        <v>4.5447</v>
       </c>
       <c r="V22" t="n">
         <v>1.8898</v>
@@ -2203,19 +2203,19 @@
         <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>33.97069999999998</v>
+        <v>53.1344</v>
       </c>
       <c r="E23" t="n">
-        <v>25.41870000000001</v>
+        <v>31.59120000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>8.5509</v>
+        <v>21.5428</v>
       </c>
       <c r="G23" t="n">
-        <v>30.27519999999999</v>
+        <v>30.2752</v>
       </c>
       <c r="H23" t="n">
-        <v>61.7551</v>
+        <v>61.75509999999998</v>
       </c>
       <c r="I23" t="n">
         <v>-31.4812</v>
@@ -2227,7 +2227,7 @@
         <v>205.5059</v>
       </c>
       <c r="L23" t="n">
-        <v>66.29719999999999</v>
+        <v>66.2972</v>
       </c>
       <c r="M23" t="n">
         <v>-241.529</v>
@@ -2245,19 +2245,19 @@
         <v>-425.5185</v>
       </c>
       <c r="R23" t="n">
-        <v>344.3774999999999</v>
+        <v>344.3775</v>
       </c>
       <c r="S23" t="n">
-        <v>31.84</v>
+        <v>51.00409999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-6.599599999999997</v>
+        <v>-0.4262000000000015</v>
       </c>
       <c r="U23" t="n">
-        <v>38.4383</v>
+        <v>51.42960000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>52.99699999999999</v>
+        <v>52.997</v>
       </c>
       <c r="W23" t="n">
         <v>185.7311</v>
